--- a/templates/hallazgos_hidrosanitario.xlsx
+++ b/templates/hallazgos_hidrosanitario.xlsx
@@ -379,13 +379,14 @@
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1">
@@ -398,7 +399,7 @@
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Columnas B-J son escritas automáticamente por el agente vía MCP (no cambiar el orden). Columnas K-M son de uso manual para hacer seguimiento a la resolución.</t>
+          <t>Columnas B-J las escribe automaticamente el agente y K-L el script (no cambiar el orden). La columna M (estado) es de uso manual para hacer seguimiento a la resolucion.</t>
         </is>
       </c>
     </row>
@@ -430,42 +431,42 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>nivel_confianza</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
           <t>referencia_normativa</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>riesgo</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>justificacion_tecnica</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>accion_correctiva</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>requiere_validacion</t>
-        </is>
-      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
+          <t>plano_referencia</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>fecha_deteccion</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
           <t>estado</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>plano_referencia</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>fecha_deteccion</t>
         </is>
       </c>
     </row>
@@ -1089,19 +1090,15 @@
   <dataValidations count="4">
     <dataValidation sqref="B5:B40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Hidrosanitario,Estructural,Arquitectonico,Electrico,Otro"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
     <dataValidation sqref="E5:E40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Crítica,Alta,Media,Baja"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="J5:J40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-      <formula2>0</formula2>
+    <dataValidation sqref="F5:F40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Alta,Media,Baja"</formula1>
     </dataValidation>
-    <dataValidation sqref="K5:K40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,En revisión,Resuelto,No aplica"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
